--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1204</v>
+        <v>1321</v>
       </c>
       <c r="B2" t="n">
-        <v>1206</v>
+        <v>1323</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1321</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="B2" t="n">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1321</v>
+        <v>1323</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,28 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>store_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ptw_dj7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>평화고시원</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>플레이더월드 대전은행점</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ptw_dj</t>
         </is>
       </c>
     </row>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -462,16 +462,16 @@
         <v>1324</v>
       </c>
       <c r="B2" t="n">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,20 +513,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>33_kd3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>목격자</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PLAY33 건대점</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>33_kd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>ptw_dj7</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>평화고시원</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>플레이더월드 대전은행점</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ptw_dj</t>
         </is>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1324</v>
+        <v>1394</v>
       </c>
       <c r="B2" t="n">
-        <v>1324</v>
+        <v>1389</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1322</v>
+        <v>1387</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,116 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>ptw_dj</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wtw_esc1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>마법사의 세계</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>월투월방탈출 서울대입구점</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>wtw_esc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>wtw_esc2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>지하감옥</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>월투월방탈출 서울대입구점</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>wtw_esc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>wtw_esc3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>드림인베이더</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>월투월방탈출 서울대입구점</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>wtw_esc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>wtw_esc4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>위험한 레시피</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>월투월방탈출 서울대입구점</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>wtw_esc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>wtw_esc5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>이상한 나라의 초대</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>월투월방탈출 서울대입구점</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>wtw_esc</t>
         </is>
       </c>
     </row>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="B2" t="n">
-        <v>1389</v>
+        <v>1407</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1387</v>
+        <v>1401</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,160 +507,6 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>store_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>33_kd3</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>목격자</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PLAY33 건대점</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>33_kd</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ptw_dj7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>평화고시원</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>플레이더월드 대전은행점</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ptw_dj</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>wtw_esc1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>마법사의 세계</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>월투월방탈출 서울대입구점</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>wtw_esc</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>wtw_esc2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>지하감옥</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>월투월방탈출 서울대입구점</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>wtw_esc</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>wtw_esc3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>드림인베이더</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>월투월방탈출 서울대입구점</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>wtw_esc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>wtw_esc4</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>위험한 레시피</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>월투월방탈출 서울대입구점</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>wtw_esc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>wtw_esc5</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>이상한 나라의 초대</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>월투월방탈출 서울대입구점</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>wtw_esc</t>
         </is>
       </c>
     </row>
@@ -675,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +541,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>osm_hd1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>osm_hd2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>osm_hd3-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>osm_hd_4-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>ptw_dsr99</t>
         </is>
       </c>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B2" t="n">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="B2" t="n">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1402</v>
+        <v>1412</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1412</v>
+        <v>1431</v>
       </c>
       <c r="B2" t="n">
-        <v>1418</v>
+        <v>1438</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>1412</v>
+        <v>1431</v>
       </c>
     </row>
   </sheetData>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>pm_hd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>ptw_dsr99</t>
         </is>
       </c>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,7 +459,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="B2" t="n">
         <v>1438</v>
@@ -468,10 +468,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>1431</v>
+        <v>1427</v>
       </c>
     </row>
   </sheetData>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,14 +569,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pm_hd1</t>
+          <t>ptw_dsr99</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ptw_dsr99</t>
+          <t>tcd_sl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tcd_sl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tcd_sl3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tcd_sl4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tcd_sl5</t>
         </is>
       </c>
     </row>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1427</v>
+        <v>1434</v>
       </c>
       <c r="B2" t="n">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1427</v>
+        <v>1434</v>
       </c>
     </row>
   </sheetData>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,41 +573,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tcd_sl1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tcd_sl2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tcd_sl3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tcd_sl4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tcd_sl5</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1434</v>
+        <v>1441</v>
       </c>
       <c r="B2" t="n">
-        <v>1440</v>
+        <v>1445</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1434</v>
+        <v>1439</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,50 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>store_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ft_str3_2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>시간의 영속성</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>판타스트릭 TGC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ft_str3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mhz_esc1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>우야</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MHZ ESCAPE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>mhz_esc</t>
         </is>
       </c>
     </row>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -1,39 +1,128 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BF74D6-EA96-4BAE-AE7D-2136C63FF269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="themes_missing_poster" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="poster_without_theme" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="summary" sheetId="1" r:id="rId1"/>
+    <sheet name="themes_missing_poster" sheetId="2" r:id="rId2"/>
+    <sheet name="poster_without_theme" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>themes_count</t>
+  </si>
+  <si>
+    <t>posters_count</t>
+  </si>
+  <si>
+    <t>missing_poster_count</t>
+  </si>
+  <si>
+    <t>extra_poster_count</t>
+  </si>
+  <si>
+    <t>both_count</t>
+  </si>
+  <si>
+    <t>theme_id</t>
+  </si>
+  <si>
+    <t>theme_name</t>
+  </si>
+  <si>
+    <t>store_name</t>
+  </si>
+  <si>
+    <t>store_id</t>
+  </si>
+  <si>
+    <t>de_as5</t>
+  </si>
+  <si>
+    <t>측신</t>
+  </si>
+  <si>
+    <t>도어이스케이프 안산점</t>
+  </si>
+  <si>
+    <t>de_as</t>
+  </si>
+  <si>
+    <t>mhz_esc1</t>
+  </si>
+  <si>
+    <t>우야</t>
+  </si>
+  <si>
+    <t>MHZ ESCAPE</t>
+  </si>
+  <si>
+    <t>mhz_esc</t>
+  </si>
+  <si>
+    <t>lds_hd99</t>
+  </si>
+  <si>
+    <t>osm_hd1-1</t>
+  </si>
+  <si>
+    <t>osm_hd2-1</t>
+  </si>
+  <si>
+    <t>osm_hd3-1</t>
+  </si>
+  <si>
+    <t>osm_hd_4-1</t>
+  </si>
+  <si>
+    <t>ptw_dsr99</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,93 +137,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,202 +461,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>themes_count</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>posters_count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>missing_poster_count</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>extra_poster_count</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>both_count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1441</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1445</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1442</v>
+      </c>
+      <c r="B2">
+        <v>1446</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
-        <v>1439</v>
+      <c r="E2">
+        <v>1440</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>theme_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>theme_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>store_name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>store_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ft_str3_2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>시간의 영속성</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>판타스트릭 TGC</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ft_str3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mhz_esc1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>우야</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MHZ ESCAPE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>mhz_esc</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>theme_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>lds_hd99</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>osm_hd1-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>osm_hd2-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>osm_hd3-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>osm_hd_4-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ptw_dsr99</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -1,128 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BF74D6-EA96-4BAE-AE7D-2136C63FF269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" r:id="rId1"/>
-    <sheet name="themes_missing_poster" sheetId="2" r:id="rId2"/>
-    <sheet name="poster_without_theme" sheetId="3" r:id="rId3"/>
+    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="themes_missing_poster" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="poster_without_theme" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>themes_count</t>
-  </si>
-  <si>
-    <t>posters_count</t>
-  </si>
-  <si>
-    <t>missing_poster_count</t>
-  </si>
-  <si>
-    <t>extra_poster_count</t>
-  </si>
-  <si>
-    <t>both_count</t>
-  </si>
-  <si>
-    <t>theme_id</t>
-  </si>
-  <si>
-    <t>theme_name</t>
-  </si>
-  <si>
-    <t>store_name</t>
-  </si>
-  <si>
-    <t>store_id</t>
-  </si>
-  <si>
-    <t>de_as5</t>
-  </si>
-  <si>
-    <t>측신</t>
-  </si>
-  <si>
-    <t>도어이스케이프 안산점</t>
-  </si>
-  <si>
-    <t>de_as</t>
-  </si>
-  <si>
-    <t>mhz_esc1</t>
-  </si>
-  <si>
-    <t>우야</t>
-  </si>
-  <si>
-    <t>MHZ ESCAPE</t>
-  </si>
-  <si>
-    <t>mhz_esc</t>
-  </si>
-  <si>
-    <t>lds_hd99</t>
-  </si>
-  <si>
-    <t>osm_hd1-1</t>
-  </si>
-  <si>
-    <t>osm_hd2-1</t>
-  </si>
-  <si>
-    <t>osm_hd3-1</t>
-  </si>
-  <si>
-    <t>osm_hd_4-1</t>
-  </si>
-  <si>
-    <t>ptw_dsr99</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -137,43 +48,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,145 +422,158 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>themes_count</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>posters_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>missing_poster_count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>extra_poster_count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>both_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1442</v>
-      </c>
-      <c r="B2">
-        <v>1446</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>6</v>
       </c>
-      <c r="E2">
-        <v>1440</v>
+      <c r="E2" t="n">
+        <v>1444</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>theme_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>theme_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>store_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>store_id</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>theme_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lds_hd99</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>osm_hd1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>osm_hd2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>osm_hd3-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>osm_hd_4-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ptw_dsr99</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B2" t="n">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1445</v>
+        <v>1461</v>
       </c>
       <c r="B2" t="n">
-        <v>1451</v>
+        <v>1467</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>1461</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B2" t="n">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1461</v>
+        <v>1463</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B2" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="B2" t="n">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1462</v>
+        <v>1466</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="B2" t="n">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,94 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>store_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fly_sw3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NO NEED FOR APOLOGIES</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The FLIGHT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>fly_sw</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fly_sw4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>양곤미용학원</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The FLIGHT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>fly_sw</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fly_sw5</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COZAZA HOTEL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The FLIGHT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fly_sw</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fly_sw6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>월야탐정</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The FLIGHT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fly_sw</t>
         </is>
       </c>
     </row>
@@ -521,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,40 +622,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lds_hd99</t>
+          <t>he_gj2_1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>osm_hd1-1</t>
+          <t>lds_hd99</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>osm_hd2-1</t>
+          <t>osm_hd1-1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>osm_hd3-1</t>
+          <t>osm_hd2-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>osm_hd_4-1</t>
+          <t>osm_hd3-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>osm_hd_4-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>ptw_dsr99</t>
         </is>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,10 +459,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B2" t="n">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -471,7 +471,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
   </sheetData>

--- a/poster_compare.xlsx
+++ b/poster_compare.xlsx
@@ -459,19 +459,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1472</v>
+        <v>1495</v>
       </c>
       <c r="B2" t="n">
-        <v>1475</v>
+        <v>1495</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>1468</v>
+        <v>1488</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,34 +513,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fly_sw3</t>
+          <t>33_dj5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NO NEED FOR APOLOGIES</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The FLIGHT</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>fly_sw</t>
+          <t>33_dj</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fly_sw4</t>
+          <t>fly_sw3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>양곤미용학원</t>
+          <t>NO NEED FOR APOLOGIES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,12 +557,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fly_sw5</t>
+          <t>fly_sw4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COZAZA HOTEL</t>
+          <t>양곤미용학원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -579,22 +579,88 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>fly_sw5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COZAZA HOTEL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The FLIGHT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fly_sw</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>fly_sw6</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>월야탐정</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>The FLIGHT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>fly_sw</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sh_djds4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>안치실</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>셜록홈즈 대전둔산점 (T.A)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sh_djds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sh_djds5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>백스테이지</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>셜록홈즈 대전둔산점 (T.A)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sh_djds</t>
         </is>
       </c>
     </row>
